--- a/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>BuffID</t>
   </si>
@@ -22,22 +22,25 @@
     <t>描述</t>
   </si>
   <si>
-    <t>是否可叠加,0:否,1:可以</t>
-  </si>
-  <si>
     <t>最多叠加层数</t>
   </si>
   <si>
+    <t>持续类型Instant,Infinit,hasDuration</t>
+  </si>
+  <si>
     <t>持续时间，0为瞬时</t>
   </si>
   <si>
+    <t>周期性, 0为没有</t>
+  </si>
+  <si>
     <t>BuffType</t>
   </si>
   <si>
-    <t>BuffEffectTypeInt</t>
-  </si>
-  <si>
-    <t>效果数值</t>
+    <t>修改的属性</t>
+  </si>
+  <si>
+    <t>效果数值, int 属性等于原来值，float 值 * 10000</t>
   </si>
   <si>
     <t>Id</t>
@@ -49,19 +52,22 @@
     <t>Description</t>
   </si>
   <si>
-    <t>IsStackable</t>
-  </si>
-  <si>
     <t>MaxStacks</t>
   </si>
   <si>
+    <t>DurationType</t>
+  </si>
+  <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>BuffTypeInt</t>
-  </si>
-  <si>
-    <t>EffectValue</t>
+    <t>Period</t>
+  </si>
+  <si>
+    <t>Numerics</t>
+  </si>
+  <si>
+    <t>EffectValues</t>
   </si>
   <si>
     <t>int</t>
@@ -73,6 +79,12 @@
     <t>double</t>
   </si>
   <si>
+    <t>uint</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>减血Buff</t>
   </si>
   <si>
@@ -89,6 +101,18 @@
   </si>
   <si>
     <t>持续增血</t>
+  </si>
+  <si>
+    <t>眩晕</t>
+  </si>
+  <si>
+    <t>眩晕3秒</t>
+  </si>
+  <si>
+    <t>无敌</t>
+  </si>
+  <si>
+    <t>无敌1秒</t>
   </si>
 </sst>
 </file>
@@ -157,7 +181,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -237,15 +261,6 @@
       <left style="thin">
         <color indexed="10"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="10"/>
-      </left>
       <right style="thin">
         <color indexed="10"/>
       </right>
@@ -261,7 +276,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -289,7 +304,7 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -301,16 +316,13 @@
     <xf numFmtId="49" fontId="5" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1403,19 +1415,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
     <col min="2" max="3" width="8.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
-    <col min="5" max="5" width="15.3516" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.8516" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.3516" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.3516" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.5" style="1" customWidth="1"/>
-    <col min="10" max="11" width="10.3516" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="6" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.3516" style="1" customWidth="1"/>
+    <col min="7" max="8" width="17.3516" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11.5" style="1" customWidth="1"/>
+    <col min="11" max="12" width="10.3516" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -1430,6 +1440,7 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2"/>
@@ -1443,6 +1454,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2"/>
@@ -1468,193 +1480,245 @@
       <c r="I3" t="s" s="9">
         <v>6</v>
       </c>
-      <c r="J3" t="s" s="7">
+      <c r="J3" t="s" s="9">
         <v>7</v>
       </c>
       <c r="K3" t="s" s="8">
         <v>8</v>
+      </c>
+      <c r="L3" t="s" s="8">
+        <v>9</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" t="s" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s" s="8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s" s="8">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s" s="8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" t="s" s="9">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s" s="9">
         <v>7</v>
       </c>
       <c r="K4" t="s" s="8">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="L4" t="s" s="8">
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" t="s" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s" s="6">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s" s="7">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s" s="13">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s" s="13">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s" s="13">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s" s="9">
         <v>19</v>
       </c>
+      <c r="G5" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s" s="9">
+        <v>21</v>
+      </c>
       <c r="I5" t="s" s="9">
-        <v>17</v>
-      </c>
-      <c r="J5" t="s" s="7">
-        <v>17</v>
-      </c>
-      <c r="K5" t="s" s="13">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="J5" t="s" s="9">
+        <v>22</v>
+      </c>
+      <c r="K5" t="s" s="9">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s" s="9">
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <v>100</v>
       </c>
-      <c r="D6" t="s" s="15">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s" s="16">
-        <v>21</v>
-      </c>
-      <c r="F6" s="14">
-        <v>1</v>
-      </c>
-      <c r="G6" s="14">
+      <c r="D6" t="s" s="14">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s" s="15">
+        <v>25</v>
+      </c>
+      <c r="F6" s="13">
         <v>5</v>
       </c>
-      <c r="H6" s="14">
+      <c r="G6" s="13">
+        <v>2</v>
+      </c>
+      <c r="H6" s="13">
         <v>5</v>
       </c>
-      <c r="I6" s="14">
-        <v>1</v>
-      </c>
-      <c r="J6" s="14">
-        <v>2</v>
-      </c>
-      <c r="K6" s="14">
-        <v>100</v>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <v>1001</v>
+      </c>
+      <c r="L6" s="13">
+        <v>-100</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="17">
+      <c r="C7" s="16">
         <v>111</v>
       </c>
-      <c r="D7" t="s" s="18">
-        <v>22</v>
-      </c>
-      <c r="E7" t="s" s="19">
-        <v>23</v>
-      </c>
-      <c r="F7" s="17">
-        <v>1</v>
-      </c>
-      <c r="G7" s="17">
+      <c r="D7" t="s" s="17">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s" s="18">
+        <v>27</v>
+      </c>
+      <c r="F7" s="16">
         <v>5</v>
       </c>
-      <c r="H7" s="17">
+      <c r="G7" s="16">
         <v>0</v>
       </c>
-      <c r="I7" s="17">
-        <v>1</v>
-      </c>
-      <c r="J7" s="17">
-        <v>1</v>
-      </c>
-      <c r="K7" s="17">
+      <c r="H7" s="16">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16">
+        <v>0</v>
+      </c>
+      <c r="J7" s="16">
+        <v>0</v>
+      </c>
+      <c r="K7" s="16">
+        <v>1002</v>
+      </c>
+      <c r="L7" s="16">
         <v>100</v>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="17">
+      <c r="C8" s="16">
         <v>222</v>
       </c>
-      <c r="D8" t="s" s="18">
-        <v>24</v>
-      </c>
-      <c r="E8" t="s" s="19">
-        <v>25</v>
-      </c>
-      <c r="F8" s="17">
-        <v>1</v>
-      </c>
-      <c r="G8" s="17">
+      <c r="D8" t="s" s="17">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s" s="18">
+        <v>29</v>
+      </c>
+      <c r="F8" s="16">
         <v>3</v>
       </c>
-      <c r="H8" s="17">
+      <c r="G8" s="16">
+        <v>2</v>
+      </c>
+      <c r="H8" s="16">
         <v>5</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="16">
         <v>0</v>
       </c>
-      <c r="J8" s="17">
-        <v>2</v>
-      </c>
-      <c r="K8" s="17">
+      <c r="J8" s="16">
+        <v>0</v>
+      </c>
+      <c r="K8" s="16">
+        <v>1001</v>
+      </c>
+      <c r="L8" s="16">
         <v>50</v>
       </c>
     </row>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="C9" s="16">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s" s="17">
+        <v>30</v>
+      </c>
+      <c r="E9" t="s" s="17">
+        <v>31</v>
+      </c>
+      <c r="F9" s="16">
+        <v>1</v>
+      </c>
+      <c r="G9" s="16">
+        <v>2</v>
+      </c>
+      <c r="H9" s="16">
+        <v>3</v>
+      </c>
+      <c r="I9" s="16">
+        <v>0</v>
+      </c>
+      <c r="J9" s="16">
+        <v>8</v>
+      </c>
       <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" ht="14" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="C10" s="16">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s" s="17">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s" s="17">
+        <v>33</v>
+      </c>
+      <c r="F10" s="16">
+        <v>1</v>
+      </c>
+      <c r="G10" s="16">
+        <v>2</v>
+      </c>
+      <c r="H10" s="16">
+        <v>2</v>
+      </c>
+      <c r="I10" s="16">
+        <v>0</v>
+      </c>
+      <c r="J10" s="16">
+        <v>4</v>
+      </c>
       <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
   <si>
     <t>BuffID</t>
   </si>
@@ -25,13 +25,13 @@
     <t>最多叠加层数</t>
   </si>
   <si>
-    <t>持续类型Instant,Infinit,hasDuration</t>
-  </si>
-  <si>
-    <t>持续时间，0为瞬时</t>
-  </si>
-  <si>
-    <t>周期性, 0为没有</t>
+    <t>持续类型0:Instant,1:Infinit,2:hasDuration</t>
+  </si>
+  <si>
+    <t>持续时间 单位毫秒</t>
+  </si>
+  <si>
+    <t>周期性, 0为没有，单位毫秒</t>
   </si>
   <si>
     <t>BuffType</t>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>double</t>
   </si>
   <si>
     <t>uint</t>
@@ -1543,19 +1540,19 @@
         <v>19</v>
       </c>
       <c r="H5" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="I5" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="J5" t="s" s="9">
         <v>21</v>
       </c>
-      <c r="I5" t="s" s="9">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s" s="9">
+      <c r="K5" t="s" s="9">
         <v>22</v>
       </c>
-      <c r="K5" t="s" s="9">
-        <v>23</v>
-      </c>
       <c r="L5" t="s" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
@@ -1565,10 +1562,10 @@
         <v>100</v>
       </c>
       <c r="D6" t="s" s="14">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s" s="15">
         <v>24</v>
-      </c>
-      <c r="E6" t="s" s="15">
-        <v>25</v>
       </c>
       <c r="F6" s="13">
         <v>5</v>
@@ -1577,7 +1574,7 @@
         <v>2</v>
       </c>
       <c r="H6" s="13">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="I6" s="13">
         <v>0</v>
@@ -1599,10 +1596,10 @@
         <v>111</v>
       </c>
       <c r="D7" t="s" s="17">
+        <v>25</v>
+      </c>
+      <c r="E7" t="s" s="18">
         <v>26</v>
-      </c>
-      <c r="E7" t="s" s="18">
-        <v>27</v>
       </c>
       <c r="F7" s="16">
         <v>5</v>
@@ -1633,10 +1630,10 @@
         <v>222</v>
       </c>
       <c r="D8" t="s" s="17">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s" s="18">
         <v>28</v>
-      </c>
-      <c r="E8" t="s" s="18">
-        <v>29</v>
       </c>
       <c r="F8" s="16">
         <v>3</v>
@@ -1645,7 +1642,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="16">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="I8" s="16">
         <v>0</v>
@@ -1667,10 +1664,10 @@
         <v>3</v>
       </c>
       <c r="D9" t="s" s="17">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s" s="17">
         <v>30</v>
-      </c>
-      <c r="E9" t="s" s="17">
-        <v>31</v>
       </c>
       <c r="F9" s="16">
         <v>1</v>
@@ -1679,7 +1676,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="16">
-        <v>3</v>
+        <v>3000</v>
       </c>
       <c r="I9" s="16">
         <v>0</v>
@@ -1697,10 +1694,10 @@
         <v>2</v>
       </c>
       <c r="D10" t="s" s="17">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s" s="17">
         <v>32</v>
-      </c>
-      <c r="E10" t="s" s="17">
-        <v>33</v>
       </c>
       <c r="F10" s="16">
         <v>1</v>
@@ -1709,7 +1706,7 @@
         <v>2</v>
       </c>
       <c r="H10" s="16">
-        <v>2</v>
+        <v>2000</v>
       </c>
       <c r="I10" s="16">
         <v>0</v>

--- a/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
   <si>
     <t>BuffID</t>
   </si>
@@ -22,6 +22,9 @@
     <t>描述</t>
   </si>
   <si>
+    <t>BuffType</t>
+  </si>
+  <si>
     <t>最多叠加层数</t>
   </si>
   <si>
@@ -34,13 +37,10 @@
     <t>周期性, 0为没有，单位毫秒</t>
   </si>
   <si>
-    <t>BuffType</t>
-  </si>
-  <si>
     <t>修改的属性</t>
   </si>
   <si>
-    <t>效果数值, int 属性等于原来值，float 值 * 10000</t>
+    <t>修改的值, int 属性设置成原来值；float 值需要 * 10000，比如0.5，这里设置成5000</t>
   </si>
   <si>
     <t>Id</t>
@@ -67,7 +67,7 @@
     <t>Numerics</t>
   </si>
   <si>
-    <t>EffectValues</t>
+    <t>NumericValues</t>
   </si>
   <si>
     <t>int</t>
@@ -76,28 +76,19 @@
     <t>string</t>
   </si>
   <si>
-    <t>uint</t>
-  </si>
-  <si>
     <t>int[]</t>
   </si>
   <si>
-    <t>减血Buff</t>
-  </si>
-  <si>
-    <t>持续减血</t>
-  </si>
-  <si>
-    <t>减蓝Buff</t>
-  </si>
-  <si>
-    <t>一次性减蓝</t>
-  </si>
-  <si>
-    <t>增血Buff</t>
-  </si>
-  <si>
-    <t>持续增血</t>
+    <t>占位buff</t>
+  </si>
+  <si>
+    <t>禁止使用，ID 0有特殊意义。这里展示用法。立刻修改int 属性-1增 加  100；float属性-2 减少 0.5</t>
+  </si>
+  <si>
+    <t>-1,-2</t>
+  </si>
+  <si>
+    <t>100,-5000</t>
   </si>
   <si>
     <t>眩晕</t>
@@ -110,6 +101,18 @@
   </si>
   <si>
     <t>无敌1秒</t>
+  </si>
+  <si>
+    <t>冰冻Debuff</t>
+  </si>
+  <si>
+    <t>被施加者冰冻3秒</t>
+  </si>
+  <si>
+    <t>超导Debuff</t>
+  </si>
+  <si>
+    <t>冰雷反应，减雷抗百分比20%</t>
   </si>
 </sst>
 </file>
@@ -273,7 +276,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -298,12 +301,12 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -318,9 +321,6 @@
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
@@ -1412,16 +1412,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
     <col min="2" max="3" width="8.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.3516" style="1" customWidth="1"/>
-    <col min="7" max="8" width="17.3516" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11.5" style="1" customWidth="1"/>
-    <col min="11" max="12" width="10.3516" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.3828" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1172" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7188" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17.3516" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.3281" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.0859" style="1" customWidth="1"/>
+    <col min="12" max="12" width="16.9219" style="1" customWidth="1"/>
     <col min="13" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1445,10 +1449,10 @@
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
+      <c r="F2" s="3"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
@@ -1468,22 +1472,22 @@
       <c r="F3" t="s" s="8">
         <v>3</v>
       </c>
-      <c r="G3" t="s" s="8">
+      <c r="G3" t="s" s="9">
         <v>4</v>
       </c>
-      <c r="H3" t="s" s="8">
+      <c r="H3" t="s" s="9">
         <v>5</v>
       </c>
       <c r="I3" t="s" s="9">
         <v>6</v>
       </c>
-      <c r="J3" t="s" s="9">
+      <c r="J3" t="s" s="8">
         <v>7</v>
       </c>
-      <c r="K3" t="s" s="8">
+      <c r="K3" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="L3" t="s" s="8">
+      <c r="L3" t="s" s="9">
         <v>9</v>
       </c>
     </row>
@@ -1500,24 +1504,24 @@
         <v>12</v>
       </c>
       <c r="F4" t="s" s="8">
+        <v>3</v>
+      </c>
+      <c r="G4" t="s" s="9">
         <v>13</v>
       </c>
-      <c r="G4" t="s" s="8">
+      <c r="H4" t="s" s="9">
         <v>14</v>
       </c>
-      <c r="H4" t="s" s="8">
+      <c r="I4" t="s" s="9">
         <v>15</v>
       </c>
-      <c r="I4" t="s" s="9">
+      <c r="J4" t="s" s="8">
         <v>16</v>
       </c>
-      <c r="J4" t="s" s="9">
-        <v>7</v>
-      </c>
-      <c r="K4" t="s" s="8">
+      <c r="K4" t="s" s="9">
         <v>17</v>
       </c>
-      <c r="L4" t="s" s="8">
+      <c r="L4" t="s" s="9">
         <v>18</v>
       </c>
     </row>
@@ -1533,48 +1537,48 @@
       <c r="E5" t="s" s="7">
         <v>20</v>
       </c>
-      <c r="F5" t="s" s="9">
+      <c r="F5" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="G5" t="s" s="9">
+      <c r="G5" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="H5" t="s" s="9">
+      <c r="H5" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="I5" t="s" s="9">
+      <c r="I5" t="s" s="8">
         <v>19</v>
       </c>
-      <c r="J5" t="s" s="9">
+      <c r="J5" t="s" s="8">
+        <v>19</v>
+      </c>
+      <c r="K5" t="s" s="8">
         <v>21</v>
       </c>
-      <c r="K5" t="s" s="9">
-        <v>22</v>
-      </c>
-      <c r="L5" t="s" s="9">
-        <v>22</v>
+      <c r="L5" t="s" s="8">
+        <v>21</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s" s="14">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s" s="14">
         <v>23</v>
       </c>
-      <c r="E6" t="s" s="15">
-        <v>24</v>
-      </c>
       <c r="F6" s="13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G6" s="13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" s="13">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="13">
         <v>0</v>
@@ -1582,140 +1586,148 @@
       <c r="J6" s="13">
         <v>0</v>
       </c>
-      <c r="K6" s="13">
-        <v>1001</v>
-      </c>
-      <c r="L6" s="13">
-        <v>-100</v>
+      <c r="K6" t="s" s="14">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s" s="14">
+        <v>25</v>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="16">
-        <v>111</v>
-      </c>
-      <c r="D7" t="s" s="17">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s" s="18">
+      <c r="C7" s="15">
+        <v>257</v>
+      </c>
+      <c r="D7" t="s" s="16">
         <v>26</v>
       </c>
-      <c r="F7" s="16">
-        <v>5</v>
-      </c>
-      <c r="G7" s="16">
+      <c r="E7" t="s" s="16">
+        <v>27</v>
+      </c>
+      <c r="F7" s="15">
+        <v>257</v>
+      </c>
+      <c r="G7" s="15">
+        <v>3</v>
+      </c>
+      <c r="H7" s="15">
+        <v>2</v>
+      </c>
+      <c r="I7" s="15">
+        <v>3000</v>
+      </c>
+      <c r="J7" s="15">
         <v>0</v>
       </c>
-      <c r="H7" s="16">
-        <v>0</v>
-      </c>
-      <c r="I7" s="16">
-        <v>0</v>
-      </c>
-      <c r="J7" s="16">
-        <v>0</v>
-      </c>
-      <c r="K7" s="16">
-        <v>1002</v>
-      </c>
-      <c r="L7" s="16">
-        <v>100</v>
-      </c>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="16">
-        <v>222</v>
-      </c>
-      <c r="D8" t="s" s="17">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s" s="18">
+      <c r="C8" s="15">
+        <v>259</v>
+      </c>
+      <c r="D8" t="s" s="16">
         <v>28</v>
       </c>
-      <c r="F8" s="16">
-        <v>3</v>
-      </c>
-      <c r="G8" s="16">
+      <c r="E8" t="s" s="16">
+        <v>29</v>
+      </c>
+      <c r="F8" s="15">
+        <v>259</v>
+      </c>
+      <c r="G8" s="15">
+        <v>10</v>
+      </c>
+      <c r="H8" s="15">
         <v>2</v>
       </c>
-      <c r="H8" s="16">
-        <v>5000</v>
-      </c>
-      <c r="I8" s="16">
+      <c r="I8" s="15">
+        <v>1000</v>
+      </c>
+      <c r="J8" s="15">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
-        <v>0</v>
-      </c>
-      <c r="K8" s="16">
-        <v>1001</v>
-      </c>
-      <c r="L8" s="16">
-        <v>50</v>
-      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
     </row>
-    <row r="9" ht="14" customHeight="1">
+    <row r="9" ht="16" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="16">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s" s="17">
-        <v>29</v>
+      <c r="C9" s="15">
+        <v>261</v>
+      </c>
+      <c r="D9" t="s" s="16">
+        <v>30</v>
       </c>
       <c r="E9" t="s" s="17">
-        <v>30</v>
-      </c>
-      <c r="F9" s="16">
+        <v>31</v>
+      </c>
+      <c r="F9" s="15">
+        <v>261</v>
+      </c>
+      <c r="G9" s="15">
         <v>1</v>
       </c>
-      <c r="G9" s="16">
+      <c r="H9" s="15">
         <v>2</v>
       </c>
-      <c r="H9" s="16">
+      <c r="I9" s="15">
         <v>3000</v>
       </c>
-      <c r="I9" s="16">
+      <c r="J9" s="15">
         <v>0</v>
-      </c>
-      <c r="J9" s="16">
-        <v>8</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
     </row>
-    <row r="10" ht="14" customHeight="1">
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
+        <v>12093</v>
+      </c>
+      <c r="D10" t="s" s="16">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s" s="17">
+        <v>33</v>
+      </c>
+      <c r="F10" s="15">
+        <v>1</v>
+      </c>
+      <c r="G10" s="15">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15">
         <v>2</v>
       </c>
-      <c r="D10" t="s" s="17">
-        <v>31</v>
-      </c>
-      <c r="E10" t="s" s="17">
-        <v>32</v>
-      </c>
-      <c r="F10" s="16">
-        <v>1</v>
-      </c>
-      <c r="G10" s="16">
-        <v>2</v>
-      </c>
-      <c r="H10" s="16">
-        <v>2000</v>
-      </c>
-      <c r="I10" s="16">
-        <v>0</v>
-      </c>
-      <c r="J10" s="16">
-        <v>4</v>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="I10" s="15">
+        <v>4000</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="15">
+        <v>12093</v>
+      </c>
+      <c r="L10" s="15">
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
   <si>
     <t>BuffID</t>
   </si>
@@ -25,12 +25,12 @@
     <t>BuffType</t>
   </si>
   <si>
+    <t>Tags</t>
+  </si>
+  <si>
     <t>最多叠加层数</t>
   </si>
   <si>
-    <t>持续类型0:Instant,1:Infinit,2:hasDuration</t>
-  </si>
-  <si>
     <t>持续时间 单位毫秒</t>
   </si>
   <si>
@@ -43,6 +43,9 @@
     <t>修改的值, int 属性设置成原来值；float 值需要 * 10000，比如0.5，这里设置成5000</t>
   </si>
   <si>
+    <t>监听的事件id</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -52,16 +55,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>MaxStacks</t>
-  </si>
-  <si>
-    <t>DurationType</t>
+    <t>MaxStack</t>
   </si>
   <si>
     <t>Duration</t>
   </si>
   <si>
-    <t>Period</t>
+    <t>Interval</t>
   </si>
   <si>
     <t>Numerics</t>
@@ -70,12 +70,18 @@
     <t>NumericValues</t>
   </si>
   <si>
+    <t>ListenEvents</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>string[]</t>
+  </si>
+  <si>
     <t>int[]</t>
   </si>
   <si>
@@ -85,6 +91,9 @@
     <t>禁止使用，ID 0有特殊意义。这里展示用法。立刻修改int 属性-1增 加  100；float属性-2 减少 0.5</t>
   </si>
   <si>
+    <t>"Test1","Test2"</t>
+  </si>
+  <si>
     <t>-1,-2</t>
   </si>
   <si>
@@ -97,16 +106,25 @@
     <t>眩晕3秒</t>
   </si>
   <si>
+    <t>"Stunned"</t>
+  </si>
+  <si>
     <t>无敌</t>
   </si>
   <si>
     <t>无敌1秒</t>
   </si>
   <si>
+    <t>"Invincible"</t>
+  </si>
+  <si>
     <t>冰冻Debuff</t>
   </si>
   <si>
     <t>被施加者冰冻3秒</t>
+  </si>
+  <si>
+    <t>"Frozen"</t>
   </si>
   <si>
     <t>超导Debuff</t>
@@ -276,7 +294,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -320,6 +338,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1412,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
@@ -1420,13 +1441,12 @@
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.3828" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.1172" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7188" style="1" customWidth="1"/>
+    <col min="7" max="8" width="11" style="1" customWidth="1"/>
     <col min="9" max="9" width="17.3516" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.3281" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.0859" style="1" customWidth="1"/>
-    <col min="12" max="12" width="16.9219" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="6" style="1" customWidth="1"/>
+    <col min="12" max="13" width="16.9219" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -1442,6 +1462,7 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2"/>
@@ -1456,6 +1477,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2"/>
@@ -1490,24 +1512,27 @@
       <c r="L3" t="s" s="9">
         <v>9</v>
       </c>
+      <c r="M3" t="s" s="9">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" t="s" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" t="s" s="8">
         <v>3</v>
       </c>
       <c r="G4" t="s" s="9">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H4" t="s" s="9">
         <v>14</v>
@@ -1523,40 +1548,46 @@
       </c>
       <c r="L4" t="s" s="9">
         <v>18</v>
+      </c>
+      <c r="M4" t="s" s="9">
+        <v>19</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" t="s" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s" s="6">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s" s="7">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s" s="8">
         <v>20</v>
       </c>
-      <c r="E5" t="s" s="7">
+      <c r="G5" t="s" s="8">
+        <v>22</v>
+      </c>
+      <c r="H5" t="s" s="8">
         <v>20</v>
       </c>
-      <c r="F5" t="s" s="8">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s" s="8">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="8">
-        <v>19</v>
-      </c>
       <c r="I5" t="s" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" t="s" s="8">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" t="s" s="8">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L5" t="s" s="8">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="M5" t="s" s="8">
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
@@ -1566,16 +1597,16 @@
         <v>0</v>
       </c>
       <c r="D6" t="s" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" s="13">
-        <v>0</v>
+      <c r="G6" t="s" s="14">
+        <v>26</v>
       </c>
       <c r="H6" s="13">
         <v>0</v>
@@ -1587,140 +1618,143 @@
         <v>0</v>
       </c>
       <c r="K6" t="s" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L6" t="s" s="14">
-        <v>25</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="M6" s="15"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="15">
-        <v>257</v>
-      </c>
-      <c r="D7" t="s" s="16">
-        <v>26</v>
-      </c>
-      <c r="E7" t="s" s="16">
-        <v>27</v>
-      </c>
-      <c r="F7" s="15">
-        <v>257</v>
-      </c>
-      <c r="G7" s="15">
+      <c r="C7" s="16">
+        <v>8193</v>
+      </c>
+      <c r="D7" t="s" s="17">
+        <v>29</v>
+      </c>
+      <c r="E7" t="s" s="17">
+        <v>30</v>
+      </c>
+      <c r="F7" s="16">
+        <v>8193</v>
+      </c>
+      <c r="G7" t="s" s="17">
+        <v>31</v>
+      </c>
+      <c r="H7" s="16">
         <v>3</v>
       </c>
-      <c r="H7" s="15">
-        <v>2</v>
-      </c>
-      <c r="I7" s="15">
+      <c r="I7" s="16">
         <v>3000</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="16">
         <v>0</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="15">
-        <v>259</v>
-      </c>
-      <c r="D8" t="s" s="16">
-        <v>28</v>
-      </c>
-      <c r="E8" t="s" s="16">
-        <v>29</v>
-      </c>
-      <c r="F8" s="15">
-        <v>259</v>
-      </c>
-      <c r="G8" s="15">
+      <c r="C8" s="16">
+        <v>8195</v>
+      </c>
+      <c r="D8" t="s" s="17">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s" s="17">
+        <v>33</v>
+      </c>
+      <c r="F8" s="16">
+        <v>8195</v>
+      </c>
+      <c r="G8" t="s" s="17">
+        <v>34</v>
+      </c>
+      <c r="H8" s="16">
         <v>10</v>
       </c>
-      <c r="H8" s="15">
-        <v>2</v>
-      </c>
-      <c r="I8" s="15">
+      <c r="I8" s="16">
         <v>1000</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J8" s="16">
         <v>0</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="15">
-        <v>261</v>
-      </c>
-      <c r="D9" t="s" s="16">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s" s="17">
-        <v>31</v>
-      </c>
-      <c r="F9" s="15">
-        <v>261</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="C9" s="16">
+        <v>8197</v>
+      </c>
+      <c r="D9" t="s" s="17">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s" s="18">
+        <v>36</v>
+      </c>
+      <c r="F9" s="16">
+        <v>8197</v>
+      </c>
+      <c r="G9" t="s" s="17">
+        <v>37</v>
+      </c>
+      <c r="H9" s="16">
         <v>1</v>
       </c>
-      <c r="H9" s="15">
-        <v>2</v>
-      </c>
-      <c r="I9" s="15">
+      <c r="I9" s="16">
         <v>3000</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J9" s="16">
         <v>0</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <v>12093</v>
       </c>
-      <c r="D10" t="s" s="16">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s" s="17">
-        <v>33</v>
-      </c>
-      <c r="F10" s="15">
+      <c r="D10" t="s" s="17">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s" s="18">
+        <v>39</v>
+      </c>
+      <c r="F10" s="16">
+        <v>128</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="16">
         <v>1</v>
       </c>
-      <c r="G10" s="15">
-        <v>1</v>
-      </c>
-      <c r="H10" s="15">
-        <v>2</v>
-      </c>
-      <c r="I10" s="15">
+      <c r="I10" s="16">
         <v>4000</v>
       </c>
       <c r="J10" s="2"/>
-      <c r="K10" s="15">
+      <c r="K10" s="16">
         <v>12093</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="16">
         <v>-2000</v>
       </c>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="17"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="18"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -1728,6 +1762,7 @@
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
   <si>
     <t>BuffID</t>
   </si>
@@ -25,6 +25,12 @@
     <t>BuffType</t>
   </si>
   <si>
+    <t>BuffHandler处理器ID</t>
+  </si>
+  <si>
+    <t>BuffNode子类类型名称，默认BuffNode。子类可以存储自定义数据，方便处理器工作。</t>
+  </si>
+  <si>
     <t>Tags</t>
   </si>
   <si>
@@ -46,6 +52,9 @@
     <t>监听的事件id</t>
   </si>
   <si>
+    <t>附加数据</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
@@ -55,6 +64,12 @@
     <t>Description</t>
   </si>
   <si>
+    <t>HandlerId</t>
+  </si>
+  <si>
+    <t>ClassName</t>
+  </si>
+  <si>
     <t>MaxStack</t>
   </si>
   <si>
@@ -64,13 +79,16 @@
     <t>Interval</t>
   </si>
   <si>
-    <t>Numerics</t>
-  </si>
-  <si>
-    <t>NumericValues</t>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>AttributeValues</t>
   </si>
   <si>
     <t>ListenEvents</t>
+  </si>
+  <si>
+    <t>CustomData</t>
   </si>
   <si>
     <t>int</t>
@@ -1433,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr defaultColWidth="6" defaultRowHeight="14.25" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
@@ -1441,12 +1459,14 @@
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.3828" style="1" customWidth="1"/>
     <col min="6" max="6" width="10.1172" style="1" customWidth="1"/>
-    <col min="7" max="8" width="11" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17.3516" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.3281" style="1" customWidth="1"/>
-    <col min="11" max="11" width="12.0859" style="1" customWidth="1"/>
-    <col min="12" max="13" width="16.9219" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="6" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5156" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.9688" style="1" customWidth="1"/>
+    <col min="9" max="10" width="11" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.3516" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.3281" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.0859" style="1" customWidth="1"/>
+    <col min="14" max="16" width="16.9219" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1">
@@ -1463,6 +1483,9 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
     </row>
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2"/>
@@ -1474,10 +1497,13 @@
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="3"/>
+      <c r="J2" s="4"/>
       <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
+      <c r="L2" s="3"/>
       <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="2"/>
@@ -1503,91 +1529,118 @@
       <c r="I3" t="s" s="9">
         <v>6</v>
       </c>
-      <c r="J3" t="s" s="8">
+      <c r="J3" t="s" s="9">
         <v>7</v>
       </c>
       <c r="K3" t="s" s="9">
         <v>8</v>
       </c>
-      <c r="L3" t="s" s="9">
+      <c r="L3" t="s" s="8">
         <v>9</v>
       </c>
       <c r="M3" t="s" s="9">
         <v>10</v>
+      </c>
+      <c r="N3" t="s" s="9">
+        <v>11</v>
+      </c>
+      <c r="O3" t="s" s="9">
+        <v>12</v>
+      </c>
+      <c r="P3" t="s" s="9">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="14" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="11"/>
       <c r="C4" t="s" s="6">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s" s="12">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s" s="8">
         <v>3</v>
       </c>
       <c r="G4" t="s" s="9">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s" s="9">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s" s="9">
-        <v>15</v>
-      </c>
-      <c r="J4" t="s" s="8">
-        <v>16</v>
+        <v>6</v>
+      </c>
+      <c r="J4" t="s" s="9">
+        <v>19</v>
       </c>
       <c r="K4" t="s" s="9">
-        <v>17</v>
-      </c>
-      <c r="L4" t="s" s="9">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="L4" t="s" s="8">
+        <v>21</v>
       </c>
       <c r="M4" t="s" s="9">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="N4" t="s" s="9">
+        <v>23</v>
+      </c>
+      <c r="O4" t="s" s="9">
+        <v>24</v>
+      </c>
+      <c r="P4" t="s" s="9">
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="14" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="5"/>
       <c r="C5" t="s" s="6">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s" s="6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="E5" t="s" s="7">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s" s="8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s" s="8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s" s="8">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I5" t="s" s="8">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s" s="8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s" s="8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s" s="8">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s" s="8">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="N5" t="s" s="8">
+        <v>29</v>
+      </c>
+      <c r="O5" t="s" s="8">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s" s="8">
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
@@ -1597,33 +1650,36 @@
         <v>0</v>
       </c>
       <c r="D6" t="s" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" t="s" s="14">
-        <v>26</v>
-      </c>
-      <c r="H6" s="13">
-        <v>0</v>
-      </c>
-      <c r="I6" s="13">
-        <v>0</v>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" t="s" s="14">
+        <v>32</v>
       </c>
       <c r="J6" s="13">
         <v>0</v>
       </c>
-      <c r="K6" t="s" s="14">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s" s="14">
-        <v>28</v>
-      </c>
-      <c r="M6" s="15"/>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" t="s" s="14">
+        <v>33</v>
+      </c>
+      <c r="N6" t="s" s="14">
+        <v>34</v>
+      </c>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="2"/>
@@ -1632,29 +1688,32 @@
         <v>8193</v>
       </c>
       <c r="D7" t="s" s="17">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s" s="17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F7" s="16">
         <v>8193</v>
       </c>
-      <c r="G7" t="s" s="17">
-        <v>31</v>
-      </c>
-      <c r="H7" s="16">
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" t="s" s="17">
+        <v>37</v>
+      </c>
+      <c r="J7" s="16">
         <v>3</v>
       </c>
-      <c r="I7" s="16">
+      <c r="K7" s="16">
         <v>3000</v>
       </c>
-      <c r="J7" s="16">
+      <c r="L7" s="16">
         <v>0</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
       <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="2"/>
@@ -1663,29 +1722,32 @@
         <v>8195</v>
       </c>
       <c r="D8" t="s" s="17">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E8" t="s" s="17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F8" s="16">
         <v>8195</v>
       </c>
-      <c r="G8" t="s" s="17">
-        <v>34</v>
-      </c>
-      <c r="H8" s="16">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" t="s" s="17">
+        <v>40</v>
+      </c>
+      <c r="J8" s="16">
         <v>10</v>
       </c>
-      <c r="I8" s="16">
+      <c r="K8" s="16">
         <v>1000</v>
       </c>
-      <c r="J8" s="16">
+      <c r="L8" s="16">
         <v>0</v>
       </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="2"/>
@@ -1694,29 +1756,32 @@
         <v>8197</v>
       </c>
       <c r="D9" t="s" s="17">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s" s="18">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F9" s="16">
         <v>8197</v>
       </c>
-      <c r="G9" t="s" s="17">
-        <v>37</v>
-      </c>
-      <c r="H9" s="16">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" t="s" s="17">
+        <v>43</v>
+      </c>
+      <c r="J9" s="16">
         <v>1</v>
       </c>
-      <c r="I9" s="16">
+      <c r="K9" s="16">
         <v>3000</v>
       </c>
-      <c r="J9" s="16">
+      <c r="L9" s="16">
         <v>0</v>
       </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
       <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="2"/>
@@ -1725,29 +1790,32 @@
         <v>12093</v>
       </c>
       <c r="D10" t="s" s="17">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s" s="18">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F10" s="16">
         <v>128</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="16">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="16">
         <v>1</v>
       </c>
-      <c r="I10" s="16">
+      <c r="K10" s="16">
         <v>4000</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="16">
+      <c r="L10" s="2"/>
+      <c r="M10" s="16">
         <v>12093</v>
       </c>
-      <c r="L10" s="16">
+      <c r="N10" s="16">
         <v>-2000</v>
       </c>
-      <c r="M10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="2"/>
@@ -1763,6 +1831,9 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
+++ b/Unity/Assets/Config/Excel/Skill/BuffConfig.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
   <si>
     <t>BuffID</t>
   </si>
@@ -49,7 +49,7 @@
     <t>修改的值, int 属性设置成原来值；float 值需要 * 10000，比如0.5，这里设置成5000</t>
   </si>
   <si>
-    <t>监听的事件id</t>
+    <t>监听的DamageStage事件</t>
   </si>
   <si>
     <t>附加数据</t>
@@ -149,6 +149,19 @@
   </si>
   <si>
     <t>冰雷反应，减雷抗百分比20%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">火力压制
+</t>
+  </si>
+  <si>
+    <t>鲁班七号被动-火力压制，被动buff的实现示例</t>
+  </si>
+  <si>
+    <t>"passive","luban"</t>
+  </si>
+  <si>
+    <t>2,4,14</t>
   </si>
 </sst>
 </file>
@@ -158,7 +171,7 @@
   <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -195,6 +208,11 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color indexed="12"/>
+      <name val="Menlo Regular"/>
     </font>
   </fonts>
   <fills count="4">
@@ -312,7 +330,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -368,7 +386,13 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -390,6 +414,7 @@
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ff92d050"/>
+      <rgbColor rgb="ff017f01"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1457,15 +1482,16 @@
     <col min="1" max="1" width="14.1719" style="1" customWidth="1"/>
     <col min="2" max="3" width="8.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.1719" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.3828" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1172" style="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5156" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.9688" style="1" customWidth="1"/>
-    <col min="9" max="10" width="11" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.4062" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.1719" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6719" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.3516" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.3281" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.0859" style="1" customWidth="1"/>
-    <col min="14" max="16" width="16.9219" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.3516" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1719" style="1" customWidth="1"/>
+    <col min="14" max="16" width="17" style="1" customWidth="1"/>
     <col min="17" max="16384" width="6" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1820,19 +1846,37 @@
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
+      <c r="C11" s="16">
+        <v>1010100</v>
+      </c>
+      <c r="D11" t="s" s="20">
+        <v>46</v>
+      </c>
+      <c r="E11" t="s" s="18">
+        <v>47</v>
+      </c>
+      <c r="F11" s="16">
+        <v>1280</v>
+      </c>
+      <c r="G11" s="16">
+        <v>10100</v>
+      </c>
       <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="I11" t="s" s="17">
+        <v>48</v>
+      </c>
+      <c r="J11" s="16">
+        <v>1</v>
+      </c>
+      <c r="K11" s="16">
+        <v>0</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="O11" t="s" s="17">
+        <v>49</v>
+      </c>
       <c r="P11" s="2"/>
     </row>
   </sheetData>
